--- a/artfynd/A 376-2023 artfynd.xlsx
+++ b/artfynd/A 376-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 376-2023 artfynd.xlsx
+++ b/artfynd/A 376-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106355589</v>
+        <v>106495628</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Hemmingsbodarna, Brynjebäcken, Kyrkås, Jmt</t>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498346.619304986</v>
+        <v>498101</v>
       </c>
       <c r="R2" t="n">
-        <v>7006692.047172769</v>
+        <v>7006426</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,24 +750,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Synobservation av en spillkråka som flög på ett par meters höjd, troligen mellan olika delar av skogen för att söka föda. I skogsbeståndet för fyndplatsen finns flertalet spår av hackspett bl.a. i form av stående död ved med större hackspår.</t>
+          <t>Skrovellav på en sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,17 +766,43 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gles och luckig skog av tall och gran med inslag av björk, gråal och sälg på fuktig till frisk-fuktig mark. Buskskikt med enbuskar. Måttlig förekomst av död ved.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -818,15 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106452957</v>
+        <v>106512287</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,42 +831,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster om Hemmingsbodarna, Brynjebäcken, Kyrkås, Jmt</t>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498093.812220043</v>
+        <v>498322</v>
       </c>
       <c r="R3" t="n">
-        <v>7006521.985194527</v>
+        <v>7006571</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,24 +895,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack-spår av tretåig hackspett på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Gott om skrovellav på en sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,6 +911,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -935,22 +922,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En sälg med 16 cm i brösthöjdsdiameter. Sälgen står i en luckig miljö nära en skoterled.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En sälg med 16 cm i brösthöjdsdiameter. Sälgen står i en luckig miljö nära en skoterled.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -968,46 +965,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106452803</v>
+        <v>106453665</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1015,10 +1003,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498077.0767186619</v>
+        <v>498099</v>
       </c>
       <c r="R4" t="n">
-        <v>7006508.450861418</v>
+        <v>7006508</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1048,24 +1036,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Lunglav vid stambasen av en smal sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1085,32 +1063,32 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>En smalväxt sälg intill en skoterled. Sälgen är skadad p.g.a. avgnagd bark.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg intill en skoterled. Sälgen är skadad p.g.a. avgnagd bark.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1128,46 +1106,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106453642</v>
+        <v>106464872</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1175,10 +1144,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498109.631512017</v>
+        <v>498098</v>
       </c>
       <c r="R5" t="n">
-        <v>7006515.203781947</v>
+        <v>7006441</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,24 +1177,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en stubbe av en knäckt sälg och låga av sälg. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1245,32 +1204,32 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>En stubbe av en knäckt smal grovbarkad sälg och dess nedfallna stam.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En stubbe av en knäckt smal grovbarkad sälg och dess nedfallna stam.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1288,19 +1247,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106453665</v>
+        <v>106497642</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1331,10 +1285,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498098.777006979</v>
+        <v>498050</v>
       </c>
       <c r="R6" t="n">
-        <v>7006507.986542933</v>
+        <v>7006441</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1364,24 +1318,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1401,7 +1345,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1414,11 +1358,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM6" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -1426,7 +1365,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1444,19 +1383,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106464872</v>
+        <v>106497877</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1487,10 +1421,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>498097.8332127155</v>
+        <v>498087</v>
       </c>
       <c r="R7" t="n">
-        <v>7006440.716473904</v>
+        <v>7006472</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1520,24 +1454,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1557,7 +1481,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Även spår av hackspettar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1572,7 +1496,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En av de grövre granarna i skogsbeståndet.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1582,7 +1506,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies # En av de grövre granarna i skogsbeståndet.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1600,46 +1524,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106496818</v>
+        <v>106498526</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1647,10 +1562,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>498115.468442524</v>
+        <v>498161</v>
       </c>
       <c r="R8" t="n">
-        <v>7006446.123959742</v>
+        <v>7006494</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1680,24 +1595,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En fin samling bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1717,32 +1622,27 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>En smal levande skadad sälg med vedsvamp och delvis död ved. Sälgen står vid en lucka i skogen.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smal levande skadad sälg med vedsvamp och delvis död ved. Sälgen står vid en lucka i skogen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1760,19 +1660,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106504501</v>
+        <v>106504278</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1803,10 +1698,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>498210.4662135264</v>
+        <v>498186</v>
       </c>
       <c r="R9" t="n">
-        <v>7006547.200923637</v>
+        <v>7006542</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1836,19 +1731,9 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1888,7 +1773,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>Ett flertal granar. Mestadels levande träd men även enstaka död gran.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1898,7 +1783,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Även gren på dött träd. # Picea abies # Ett flertal granar. Mestadels levande träd men även enstaka död gran.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1916,19 +1801,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106504278</v>
+        <v>106504501</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1959,10 +1839,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>498186.5024317834</v>
+        <v>498210</v>
       </c>
       <c r="R10" t="n">
-        <v>7006541.796634975</v>
+        <v>7006547</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1992,19 +1872,9 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -2044,7 +1914,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Ett flertal granar. Mestadels levande träd men även enstaka död gran.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2054,7 +1924,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Även gren på dött träd. # Picea abies # Ett flertal granar. Mestadels levande träd men även enstaka död gran.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2072,19 +1942,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106498526</v>
+        <v>106504906</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2115,10 +1980,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>498161.1578862062</v>
+        <v>498267</v>
       </c>
       <c r="R11" t="n">
-        <v>7006493.503172393</v>
+        <v>7006575</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2148,24 +2013,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2185,7 +2040,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2223,19 +2078,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106497642</v>
+        <v>106511438</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2266,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>498049.9104240927</v>
+        <v>498308</v>
       </c>
       <c r="R12" t="n">
-        <v>7006441.196528297</v>
+        <v>7006606</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2299,19 +2149,9 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2336,7 +2176,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2374,19 +2214,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106497877</v>
+        <v>106511533</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2417,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>498087.4532532557</v>
+        <v>498308</v>
       </c>
       <c r="R13" t="n">
-        <v>7006471.874943718</v>
+        <v>7006619</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2450,24 +2285,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxta bålar av garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2487,7 +2312,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Även spår av hackspettar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2502,7 +2327,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En av de grövre granarna i skogsbeståndet.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2512,7 +2337,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # En av de grövre granarna i skogsbeståndet.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2530,46 +2355,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106495628</v>
+        <v>106513240</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2577,10 +2393,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>498100.9891862479</v>
+        <v>498322</v>
       </c>
       <c r="R14" t="n">
-        <v>7006425.815565346</v>
+        <v>7006571</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2610,24 +2426,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Skrovellav på en sälg där det även växer lunglav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2647,32 +2453,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2690,46 +2491,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106495460</v>
+        <v>106531444</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2737,10 +2529,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498100.9891862479</v>
+        <v>498283</v>
       </c>
       <c r="R15" t="n">
-        <v>7006425.815565346</v>
+        <v>7006532</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2770,24 +2562,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Måttlig påväxt av lunglav på en sälg där det även växer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på fler granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2807,32 +2589,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Gles och luckig granskog med inslag av björk på fuktig mark. Här finns mestadels klenvuxna träd.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2850,19 +2632,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106504906</v>
+        <v>106532964</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2893,10 +2670,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498266.9924093342</v>
+        <v>498253</v>
       </c>
       <c r="R16" t="n">
-        <v>7006575.161160219</v>
+        <v>7006530</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2926,24 +2703,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på fler granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2963,7 +2730,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Gles och luckig granskog med inslag av björk på fuktig och frisk-fuktig mark. Här finns mestadels klenvuxna träd.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2976,6 +2743,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM16" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2983,7 +2755,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3001,37 +2773,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106534776</v>
+        <v>106535149</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3048,10 +2815,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>498179.2420192157</v>
+        <v>498168</v>
       </c>
       <c r="R17" t="n">
-        <v>7006493.944408531</v>
+        <v>7006505</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -3081,24 +2848,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gott om lunglav på en gammal sälg. Flertalet bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3118,32 +2875,32 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk till frisk-fuktig och fuktig mark. Skogsbeståndet klassas som sumpskog enligt Skogsstyrelsen. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>En gammal sälg med 28 cm i brösthöjdsdiameter.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal sälg med 28 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3161,19 +2918,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106535149</v>
+        <v>106535691</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -3196,11 +2948,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3208,10 +2956,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>498167.9457408596</v>
+        <v>498006</v>
       </c>
       <c r="R18" t="n">
-        <v>7006504.786247115</v>
+        <v>7006504</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3241,24 +2989,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3278,7 +3016,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk till frisk-fuktig och fuktig mark. Skogsbeståndet klassas som sumpskog enligt Skogsstyrelsen. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig, blöt och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3291,11 +3029,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM18" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3303,7 +3036,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3321,19 +3054,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106511533</v>
+        <v>106535777</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3364,10 +3092,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498308.6069687798</v>
+        <v>498010</v>
       </c>
       <c r="R19" t="n">
-        <v>7006618.479611618</v>
+        <v>7006534</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3397,24 +3125,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Långväxta bålar av garnlav på flera granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3434,7 +3152,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3447,11 +3165,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM19" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3459,7 +3172,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3477,19 +3190,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106531444</v>
+        <v>106535838</v>
       </c>
       <c r="B20" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3520,10 +3228,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498282.340515527</v>
+        <v>498043</v>
       </c>
       <c r="R20" t="n">
-        <v>7006532.263350909</v>
+        <v>7006594</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3553,24 +3261,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på fler granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Riklig påväxt av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3590,7 +3288,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Gles och luckig granskog med inslag av björk på fuktig mark. Här finns mestadels klenvuxna träd.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig, frisk-fuktig och blöt mark. Skogsbeståndet klassas som sumpskog enligt Skogsstyrelsen. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3603,11 +3301,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM20" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3615,7 +3308,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3633,19 +3326,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106532964</v>
+        <v>106535843</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3676,10 +3364,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498252.5010089275</v>
+        <v>498024</v>
       </c>
       <c r="R21" t="n">
-        <v>7006529.570515951</v>
+        <v>7006591</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3709,24 +3397,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på fler granar. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3746,7 +3424,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Gles och luckig granskog med inslag av björk på fuktig och frisk-fuktig mark. Här finns mestadels klenvuxna träd.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från någon cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3759,11 +3437,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM21" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3771,7 +3444,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3789,46 +3462,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106511032</v>
+        <v>106544194</v>
       </c>
       <c r="B22" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3836,10 +3500,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>498308.6001145109</v>
+        <v>498011</v>
       </c>
       <c r="R22" t="n">
-        <v>7006605.387231935</v>
+        <v>7006564</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3869,24 +3533,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Stuplav på stambasen av en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3906,32 +3560,32 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från någon cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>En levande sälg med 20 cm i brösthöjdsdiameter. I sälgen finns vedsvamp och uthackade bohål i del av trädet som utgörs av död ved.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En levande sälg med 20 cm i brösthöjdsdiameter. I sälgen finns vedsvamp och uthackade bohål i del av trädet som utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3949,19 +3603,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106535691</v>
+        <v>106544255</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3992,10 +3641,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>498006.0947589126</v>
+        <v>497949</v>
       </c>
       <c r="R23" t="n">
-        <v>7006503.527648161</v>
+        <v>7006573</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -4025,24 +3674,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på flera granar. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -4062,7 +3701,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig, blöt och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk-fuktig och frisk mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4075,6 +3714,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM23" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -4082,7 +3726,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4100,19 +3744,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106511438</v>
+        <v>106544344</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -4143,10 +3782,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>498308.6001145109</v>
+        <v>497845</v>
       </c>
       <c r="R24" t="n">
-        <v>7006605.387231935</v>
+        <v>7006599</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -4176,24 +3815,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på flera granar. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4213,7 +3842,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -4251,19 +3880,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106535777</v>
+        <v>106544505</v>
       </c>
       <c r="B25" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -4294,10 +3918,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>498010.6343399739</v>
+        <v>497807</v>
       </c>
       <c r="R25" t="n">
-        <v>7006533.773644323</v>
+        <v>7006629</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4327,24 +3951,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4364,7 +3978,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -4402,19 +4016,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106513240</v>
+        <v>106544539</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -4445,10 +4054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>498322.1445002424</v>
+        <v>497826</v>
       </c>
       <c r="R26" t="n">
-        <v>7006570.617377875</v>
+        <v>7006608</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4478,24 +4087,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4515,7 +4114,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -4553,46 +4152,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106512287</v>
+        <v>106544739</v>
       </c>
       <c r="B27" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4600,10 +4190,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>498322.1445002424</v>
+        <v>497858</v>
       </c>
       <c r="R27" t="n">
-        <v>7006570.617377875</v>
+        <v>7006576</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4633,24 +4223,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om skrovellav på en sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Garnlav på gran. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4670,32 +4250,27 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>En sälg med 16 cm i brösthöjdsdiameter. Sälgen står i en luckig miljö nära en skoterled.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En sälg med 16 cm i brösthöjdsdiameter. Sälgen står i en luckig miljö nära en skoterled.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4713,19 +4288,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106535843</v>
+        <v>106544834</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -4756,10 +4326,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>498023.7800604833</v>
+        <v>497897</v>
       </c>
       <c r="R28" t="n">
-        <v>7006591.102068705</v>
+        <v>7006564</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4789,24 +4359,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Långväxt garnlav på gran. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4826,7 +4386,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från någon cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4864,15 +4424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106544194</v>
+        <v>106452803</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4880,26 +4435,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4907,10 +4466,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>498011.1047744328</v>
+        <v>498077</v>
       </c>
       <c r="R29" t="n">
-        <v>7006563.570398536</v>
+        <v>7006509</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4940,24 +4499,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Lunglav vid stambasen av en smal sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4977,32 +4526,32 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från någon cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En smalväxt sälg intill en skoterled. Sälgen är skadad p.g.a. avgnagd bark.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg intill en skoterled. Sälgen är skadad p.g.a. avgnagd bark.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5020,15 +4569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106535838</v>
+        <v>106453642</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5036,26 +4580,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -5063,10 +4611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>498042.7694740324</v>
+        <v>498110</v>
       </c>
       <c r="R30" t="n">
-        <v>7006594.250758512</v>
+        <v>7006515</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -5096,24 +4644,14 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Riklig påväxt av garnlav på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+          <t>Gott om lunglav på en stubbe av en knäckt sälg och låga av sälg. Vissa bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5133,27 +4671,32 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på fuktig, frisk-fuktig och blöt mark. Skogsbeståndet klassas som sumpskog enligt Skogsstyrelsen. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>En stubbe av en knäckt smal grovbarkad sälg och dess nedfallna stam.</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En stubbe av en knäckt smal grovbarkad sälg och dess nedfallna stam.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5168,6 +4711,1130 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>106495460</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>498101</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7006426</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Måttlig påväxt av lunglav på en sälg där det även växer skrovellav. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En sälg med 14 cm i brösthöjdsdiameter. Sälgen är delvis skadad med knäckt gren/stam och står vid en lucka i skogen.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>106496818</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>498116</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7006446</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>En fin samling bålar av lunglav på sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk, frisk-fuktig och fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>En smal levande skadad sälg med vedsvamp och delvis död ved. Sälgen står vid en lucka i skogen.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En smal levande skadad sälg med vedsvamp och delvis död ved. Sälgen står vid en lucka i skogen.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>106534776</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>498179</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7006494</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om lunglav på en gammal sälg. Flertalet bålar är fertila med apothecier. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>En gammal sälg med 28 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal sälg med 28 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>106511032</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>498308</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7006606</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Stuplav på stambasen av en gammal sälg. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig till frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>En levande sälg med 20 cm i brösthöjdsdiameter. I sälgen finns vedsvamp och uthackade bohål i del av trädet som utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En levande sälg med 20 cm i brösthöjdsdiameter. I sälgen finns vedsvamp och uthackade bohål i del av trädet som utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>106543077</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>497822</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7006636</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Måttlig mängd stuplav på en sälg. Fyndplatsen finns inom en yta som markerats med naturvärde av Skogsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>En något smalare sälg.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En något smalare sälg.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>106355589</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Brynjebäcken, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>498346</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7006692</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Synobservation av en spillkråka som flög på ett par meters höjd, troligen mellan olika delar av skogen för att söka föda. I skogsbeståndet för fyndplatsen finns flertalet spår av hackspett bl.a. i form av stående död ved med större hackspår.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Gles och luckig skog av tall och gran med inslag av björk, gråal och sälg på fuktig till frisk-fuktig mark. Buskskikt med enbuskar. Måttlig förekomst av död ved.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>106452957</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Brynjebäcken, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>498094</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7006522</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack-spår av tretåig hackspett på gran. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 376-2023.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk och frisk-fuktig mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>106504945</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Väster om Hemmingsbodarna, Brynjebäcken, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>498356</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7006614</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad och luckig granskog med inslag av tall, björk, gråal och sälg på frisk-fuktig och frisk mark. Här finns träd med olika ålder och grovlek från några cm till omkring 60 cm i brösthöjdsdiameter för tall. Bitvis gott om klenvuxna granar. Buskskikt med enbuskar och fältskikt med inslag av högörter. Måttlig förekomst av stående och liggande död ved. Spår av tidigare brand i form av kolade stubbar. Gamla mossöverväxta stubbar vittnar här om gamla tiders skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 376-2023 artfynd.xlsx
+++ b/artfynd/A 376-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106495628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -962,6 +972,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106512287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1103,6 +1118,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106453665</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1244,6 +1264,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106464872</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1380,6 +1405,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106497642</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1521,6 +1551,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106497877</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1657,6 +1692,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106498526</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1798,6 +1838,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106504278</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1939,6 +1984,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106504501</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2075,6 +2125,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106504906</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2211,6 +2266,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106511438</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2352,6 +2412,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106511533</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2488,6 +2553,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106513240</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2629,6 +2699,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106531444</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2770,6 +2845,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106532964</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2915,6 +2995,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106535149</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3051,6 +3136,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106535691</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3187,6 +3277,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106535777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3323,6 +3418,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106535838</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3459,6 +3559,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106535843</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3600,6 +3705,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544194</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3741,6 +3851,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544255</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3877,6 +3992,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544344</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4013,6 +4133,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544505</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4149,6 +4274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544539</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4285,6 +4415,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544739</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4421,6 +4556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106544834</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4566,6 +4706,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106452803</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4711,6 +4856,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106453642</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4856,6 +5006,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106495460</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -5001,6 +5156,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106496818</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5146,6 +5306,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106534776</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5291,6 +5456,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106511032</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5432,6 +5602,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106543077</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5560,6 +5735,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106355589</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5695,6 +5875,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106452957</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5835,8 +6020,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106504945</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>